--- a/spreadsheet_auditor/demo/demo_bad_budget.xlsx
+++ b/spreadsheet_auditor/demo/demo_bad_budget.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Budget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,15 +543,15 @@
         </is>
       </c>
       <c r="B6">
-        <f>SUM(B2:B5)+B5</f>
+        <f>SUM(B4:B5)+B5</f>
         <v/>
       </c>
       <c r="C6">
-        <f>SUM(C2:C5)</f>
+        <f>SUM(C4:C5)</f>
         <v/>
       </c>
       <c r="D6">
-        <f>SUM(D2:D5)</f>
+        <f>SUM(D4:D5)</f>
         <v/>
       </c>
       <c r="E6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>SUM(B7:B9)</f>
+        <f>SUM(B7:B8)</f>
         <v/>
       </c>
       <c r="C10">
@@ -644,19 +644,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grand total</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="B11">
-        <f>SUM(B2:B8)</f>
+        <f>B6-B10</f>
         <v/>
       </c>
       <c r="C11">
-        <f>SUM(C2:C9)</f>
+        <f>C6-C10</f>
         <v/>
       </c>
       <c r="D11">
-        <f>SUM(D2:D9)</f>
+        <f>D6-D10</f>
         <v/>
       </c>
       <c r="E11">
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,38 @@
         <v/>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Owner lookup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>VLOOKUP(B2,Budget!A17:B19,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bonus accrual</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>SUM(Budget!B20:B20)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
